--- a/artfynd/A 30716-2025 artfynd.xlsx
+++ b/artfynd/A 30716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103226845</v>
+        <v>103226832</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627083.1875817324</v>
+        <v>627081</v>
       </c>
       <c r="R2" t="n">
-        <v>6654738.423002371</v>
+        <v>6654740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,53 +776,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103226841</v>
+        <v>122704620</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lortmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626942.752167515</v>
+        <v>626866</v>
       </c>
       <c r="R3" t="n">
-        <v>6654609.468485853</v>
+        <v>6654664</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +853,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,57 +879,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Garmo</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Garmo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Lortmossen</t>
-        </is>
-      </c>
+          <t>Gabriel Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103226832</v>
+        <v>103226841</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627081.1158250824</v>
+        <v>626942</v>
       </c>
       <c r="R4" t="n">
-        <v>6654740.353415578</v>
+        <v>6654610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +968,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,65 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122704620</v>
+        <v>103226845</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lortmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626866</v>
+        <v>627083</v>
       </c>
       <c r="R5" t="n">
-        <v>6654664</v>
+        <v>6654738</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,24 +1082,129 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Erik Garmo</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Erik Garmo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lortmossen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114700589</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lortmossen (10), Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626943</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6654609</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>C-Upp-0832</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Garmo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
